--- a/Result/profitability/3310.xlsx
+++ b/Result/profitability/3310.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>0.62625</v>
+        <v>0.67125</v>
       </c>
       <c r="N2" t="n">
-        <v>22.035</v>
+        <v>21.88</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4737499999999999</v>
+        <v>0.5687500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>21.1675</v>
+        <v>21.31625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.40875</v>
+        <v>0.27</v>
       </c>
       <c r="N4" t="n">
-        <v>19.74875</v>
+        <v>19.6325</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0675</v>
+        <v>0.06500000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>14.185</v>
+        <v>13.70625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1375</v>
+        <v>-0.04874999999999997</v>
       </c>
       <c r="N6" t="n">
-        <v>11.29625</v>
+        <v>11.5325</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.27625</v>
+        <v>-0.18375</v>
       </c>
       <c r="N7" t="n">
-        <v>9.504999999999999</v>
+        <v>9.70125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3437499999999999</v>
+        <v>-0.23</v>
       </c>
       <c r="N8" t="n">
-        <v>8.975000000000001</v>
+        <v>9.141249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>703</v>
+      </c>
+      <c r="D75" t="n">
+        <v>540</v>
+      </c>
+      <c r="E75" t="n">
+        <v>162</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>81</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.51%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>104</v>
+      </c>
+      <c r="K75" t="n">
+        <v>94</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.82125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.1325</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9099999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.676470588235294</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.329999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06100917431192654</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>5.578947368421052</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.830000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1420623145400595</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
